--- a/data/caiso_loads/raw/validation_data/historical-ems-hourly-load-for-march-2025.xlsx
+++ b/data/caiso_loads/raw/validation_data/historical-ems-hourly-load-for-march-2025.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr showInkAnnotation="0" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://records.oa.caiso.com/sites/MID/ID/RAP/Shared Documents/Records/Regulatory/CAISO/2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brian\Documents\Coding\CAISO_load_forecasting\data\caiso_loads\raw\validation_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FE795E-DA6A-45CE-BF4B-4D7EF1606CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23940" windowHeight="9240"/>
+    <workbookView xWindow="-28920" yWindow="5175" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMS Hourly Load for Jan 2024" sheetId="2" r:id="rId1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Date</t>
   </si>
@@ -61,14 +62,11 @@
   <si>
     <t>CAISO Public</t>
   </si>
-  <si>
-    <t>Spring DST change occurs on March 9 in HE2</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -188,16 +186,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G744" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" tableBorderDxfId="7">
-  <autoFilter ref="A1:G744"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G744" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" tableBorderDxfId="7">
+  <autoFilter ref="A1:G744" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="2" name="Date" dataDxfId="6"/>
-    <tableColumn id="3" name="HR" dataDxfId="5"/>
-    <tableColumn id="6" name="PGE" dataDxfId="4"/>
-    <tableColumn id="7" name="SCE" dataDxfId="3"/>
-    <tableColumn id="9" name="SDGE" dataDxfId="2"/>
-    <tableColumn id="10" name="VEA" dataDxfId="1"/>
-    <tableColumn id="11" name="CAISO" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="HR" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PGE" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="SCE" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="SDGE" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="VEA" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CAISO" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -465,15 +463,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J746"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -495,11 +493,9 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>45717</v>
       </c>
@@ -525,7 +521,7 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45717</v>
       </c>
@@ -551,7 +547,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45717</v>
       </c>
@@ -577,7 +573,7 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45717</v>
       </c>
@@ -600,7 +596,7 @@
         <v>18823.379708</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45717</v>
       </c>
@@ -623,7 +619,7 @@
         <v>18882.959535000002</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45717</v>
       </c>
@@ -646,7 +642,7 @@
         <v>19393.670512000001</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45717</v>
       </c>
@@ -669,7 +665,7 @@
         <v>20041.017956</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45717</v>
       </c>
@@ -692,7 +688,7 @@
         <v>20472.483786000001</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45717</v>
       </c>
@@ -715,7 +711,7 @@
         <v>20744.3884898</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45717</v>
       </c>
@@ -738,7 +734,7 @@
         <v>20892.443639199999</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45717</v>
       </c>
@@ -761,7 +757,7 @@
         <v>21387.632227999999</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45717</v>
       </c>
@@ -784,7 +780,7 @@
         <v>21850.178833000002</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45717</v>
       </c>
@@ -807,7 +803,7 @@
         <v>21300.0957539999</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45717</v>
       </c>
@@ -830,7 +826,7 @@
         <v>21339.407039000002</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45717</v>
       </c>
@@ -853,7 +849,7 @@
         <v>21313.619348</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45717</v>
       </c>
@@ -876,7 +872,7 @@
         <v>21360.471328</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45717</v>
       </c>
@@ -899,7 +895,7 @@
         <v>20929.607911399999</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45717</v>
       </c>
@@ -922,7 +918,7 @@
         <v>22392.125293999899</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45717</v>
       </c>
@@ -945,7 +941,7 @@
         <v>23730.957265000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45717</v>
       </c>
@@ -968,7 +964,7 @@
         <v>23447.089564000002</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45717</v>
       </c>
@@ -991,7 +987,7 @@
         <v>22973.942727000001</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45717</v>
       </c>
@@ -1014,7 +1010,7 @@
         <v>22388.477272</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45717</v>
       </c>
@@ -1037,7 +1033,7 @@
         <v>21518.067292</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45717</v>
       </c>
@@ -1060,7 +1056,7 @@
         <v>20611.085034</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45718</v>
       </c>
@@ -1083,7 +1079,7 @@
         <v>20350.583337</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45718</v>
       </c>
@@ -1106,7 +1102,7 @@
         <v>19482.702754999998</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45718</v>
       </c>
@@ -1129,7 +1125,7 @@
         <v>19122.5951189999</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45718</v>
       </c>
@@ -1152,7 +1148,7 @@
         <v>18739.28</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45718</v>
       </c>
@@ -1175,7 +1171,7 @@
         <v>18694.293898</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45718</v>
       </c>
@@ -1198,7 +1194,7 @@
         <v>18988.79997</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45718</v>
       </c>
@@ -1221,7 +1217,7 @@
         <v>19501.918548000001</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45718</v>
       </c>
@@ -1244,7 +1240,7 @@
         <v>20715.270404999999</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45718</v>
       </c>
@@ -1267,7 +1263,7 @@
         <v>22701.003839000001</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>45718</v>
       </c>
@@ -1290,7 +1286,7 @@
         <v>22879.002877399998</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>45718</v>
       </c>
@@ -1313,7 +1309,7 @@
         <v>22710.108669199999</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45718</v>
       </c>
@@ -1336,7 +1332,7 @@
         <v>22163.248470300001</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>45718</v>
       </c>
@@ -1359,7 +1355,7 @@
         <v>21055.378234799999</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>45718</v>
       </c>
@@ -1382,7 +1378,7 @@
         <v>20836.653346999999</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>45718</v>
       </c>
@@ -1405,7 +1401,7 @@
         <v>19384.240571999999</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>45718</v>
       </c>
@@ -1428,7 +1424,7 @@
         <v>19212.789313000001</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>45718</v>
       </c>
@@ -1451,7 +1447,7 @@
         <v>20395.982355319898</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>45718</v>
       </c>
@@ -1474,7 +1470,7 @@
         <v>22627.490284</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>45718</v>
       </c>
@@ -1497,7 +1493,7 @@
         <v>24292.050071000001</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>45718</v>
       </c>
@@ -1520,7 +1516,7 @@
         <v>24223.527730999998</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45718</v>
       </c>
@@ -1543,7 +1539,7 @@
         <v>23771.354632999999</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45718</v>
       </c>
@@ -1566,7 +1562,7 @@
         <v>23290.294536000001</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>45718</v>
       </c>
@@ -1589,7 +1585,7 @@
         <v>22217.678818</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>45718</v>
       </c>
@@ -1612,7 +1608,7 @@
         <v>20905.674382000001</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>45719</v>
       </c>
@@ -1635,7 +1631,7 @@
         <v>20572.475522000001</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>45719</v>
       </c>
@@ -1658,7 +1654,7 @@
         <v>20040.171668999999</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>45719</v>
       </c>
@@ -1681,7 +1677,7 @@
         <v>19562.492782000001</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>45719</v>
       </c>
@@ -1704,7 +1700,7 @@
         <v>19677.016077</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>45719</v>
       </c>
@@ -1727,7 +1723,7 @@
         <v>20263.505400999999</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>45719</v>
       </c>
@@ -1750,7 +1746,7 @@
         <v>22014.837040999999</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>45719</v>
       </c>
@@ -1773,7 +1769,7 @@
         <v>23963.981596000001</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>45719</v>
       </c>
@@ -1796,7 +1792,7 @@
         <v>25077.945856999999</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>45719</v>
       </c>
@@ -1819,7 +1815,7 @@
         <v>25184.902773999998</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>45719</v>
       </c>
@@ -1842,7 +1838,7 @@
         <v>24032.765809999899</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>45719</v>
       </c>
@@ -1865,7 +1861,7 @@
         <v>23578.737830999999</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>45719</v>
       </c>
@@ -1888,7 +1884,7 @@
         <v>22824.300352999999</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>45719</v>
       </c>
@@ -1911,7 +1907,7 @@
         <v>22693.057723999998</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>45719</v>
       </c>
@@ -1934,7 +1930,7 @@
         <v>22059.782593</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>45719</v>
       </c>
@@ -1957,7 +1953,7 @@
         <v>21637.198041</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>45719</v>
       </c>
@@ -1980,7 +1976,7 @@
         <v>21635.571057000001</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>45719</v>
       </c>
@@ -2003,7 +1999,7 @@
         <v>21960.742420899998</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>45719</v>
       </c>
@@ -2026,7 +2022,7 @@
         <v>24415.1228979999</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>45719</v>
       </c>
@@ -2049,7 +2045,7 @@
         <v>26183.626311</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>45719</v>
       </c>
@@ -2072,7 +2068,7 @@
         <v>26172.760537999999</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>45719</v>
       </c>
@@ -2095,7 +2091,7 @@
         <v>25701.614861999999</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>45719</v>
       </c>
@@ -2118,7 +2114,7 @@
         <v>25143.2922369999</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>45719</v>
       </c>
@@ -2141,7 +2137,7 @@
         <v>23707.295010999998</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>45719</v>
       </c>
@@ -2164,7 +2160,7 @@
         <v>22366.170270999999</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>45720</v>
       </c>
@@ -2187,7 +2183,7 @@
         <v>21991.431445999999</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>45720</v>
       </c>
@@ -2210,7 +2206,7 @@
         <v>21511.201609</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>45720</v>
       </c>
@@ -2233,7 +2229,7 @@
         <v>20966.623204</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>45720</v>
       </c>
@@ -2256,7 +2252,7 @@
         <v>20855.993547999999</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>45720</v>
       </c>
@@ -2279,7 +2275,7 @@
         <v>21023.021069999999</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>45720</v>
       </c>
@@ -2302,7 +2298,7 @@
         <v>22418.160489000002</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>45720</v>
       </c>
@@ -2325,7 +2321,7 @@
         <v>24659.766011</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>45720</v>
       </c>
@@ -2348,7 +2344,7 @@
         <v>26142.531348</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>45720</v>
       </c>
@@ -2371,7 +2367,7 @@
         <v>26944.560784500001</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>45720</v>
       </c>
@@ -2394,7 +2390,7 @@
         <v>26406.536112400001</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>45720</v>
       </c>
@@ -2417,7 +2413,7 @@
         <v>25153.265953900001</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>45720</v>
       </c>
@@ -2440,7 +2436,7 @@
         <v>23881.520417899999</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>45720</v>
       </c>
@@ -2463,7 +2459,7 @@
         <v>22324.4563385</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>45720</v>
       </c>
@@ -2486,7 +2482,7 @@
         <v>21866.350253299999</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>45720</v>
       </c>
@@ -2509,7 +2505,7 @@
         <v>21846.5390741999</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>45720</v>
       </c>
@@ -2532,7 +2528,7 @@
         <v>22174.345564300002</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>45720</v>
       </c>
@@ -2555,7 +2551,7 @@
         <v>23007.4251411</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>45720</v>
       </c>
@@ -2578,7 +2574,7 @@
         <v>24809.4273489999</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>45720</v>
       </c>
@@ -2601,7 +2597,7 @@
         <v>26046.121026000001</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>45720</v>
       </c>
@@ -2624,7 +2620,7 @@
         <v>25815.891706999999</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>45720</v>
       </c>
@@ -2647,7 +2643,7 @@
         <v>25253.433400000002</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>45720</v>
       </c>
@@ -2670,7 +2666,7 @@
         <v>24359.417152000002</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>45720</v>
       </c>
@@ -2693,7 +2689,7 @@
         <v>22946.385907</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>45720</v>
       </c>
@@ -2716,7 +2712,7 @@
         <v>21518.931178999999</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>45721</v>
       </c>
@@ -2739,7 +2735,7 @@
         <v>21287.395651999999</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>45721</v>
       </c>
@@ -2762,7 +2758,7 @@
         <v>20819.582975000001</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>45721</v>
       </c>
@@ -2785,7 +2781,7 @@
         <v>20279.9730849999</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>45721</v>
       </c>
@@ -2808,7 +2804,7 @@
         <v>20023.835461999999</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>45721</v>
       </c>
@@ -2831,7 +2827,7 @@
         <v>20744.111688999899</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>45721</v>
       </c>
@@ -2854,7 +2850,7 @@
         <v>22344.050491000002</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>45721</v>
       </c>
@@ -2877,7 +2873,7 @@
         <v>24175.864115999899</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>45721</v>
       </c>
@@ -2900,7 +2896,7 @@
         <v>25330.703153999999</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>45721</v>
       </c>
@@ -2923,7 +2919,7 @@
         <v>26418.501024000001</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>45721</v>
       </c>
@@ -2946,7 +2942,7 @@
         <v>26555.160599999999</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>45721</v>
       </c>
@@ -2969,7 +2965,7 @@
         <v>26292.836288999999</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>45721</v>
       </c>
@@ -2992,7 +2988,7 @@
         <v>26922.623516</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>45721</v>
       </c>
@@ -3015,7 +3011,7 @@
         <v>26268.216930999999</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>45721</v>
       </c>
@@ -3038,7 +3034,7 @@
         <v>25797.579443999999</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>45721</v>
       </c>
@@ -3061,7 +3057,7 @@
         <v>25744.806811999999</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>45721</v>
       </c>
@@ -3084,7 +3080,7 @@
         <v>26125.051559</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>45721</v>
       </c>
@@ -3107,7 +3103,7 @@
         <v>25724.295160000001</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>45721</v>
       </c>
@@ -3130,7 +3126,7 @@
         <v>26082.607195999899</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>45721</v>
       </c>
@@ -3153,7 +3149,7 @@
         <v>27350.0062</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>45721</v>
       </c>
@@ -3176,7 +3172,7 @@
         <v>27023.476562</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>45721</v>
       </c>
@@ -3199,7 +3195,7 @@
         <v>26178.191920000001</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>45721</v>
       </c>
@@ -3222,7 +3218,7 @@
         <v>25339.772715999999</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>45721</v>
       </c>
@@ -3245,7 +3241,7 @@
         <v>24442.58007</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>45721</v>
       </c>
@@ -3268,7 +3264,7 @@
         <v>23263.215215</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>45722</v>
       </c>
@@ -3291,7 +3287,7 @@
         <v>22559.790751</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>45722</v>
       </c>
@@ -3314,7 +3310,7 @@
         <v>21925.013126000002</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>45722</v>
       </c>
@@ -3337,7 +3333,7 @@
         <v>21837.268319999999</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
         <v>45722</v>
       </c>
@@ -3360,7 +3356,7 @@
         <v>21066.715874000001</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>45722</v>
       </c>
@@ -3383,7 +3379,7 @@
         <v>21382.886719999999</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>45722</v>
       </c>
@@ -3406,7 +3402,7 @@
         <v>22712.586798</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>45722</v>
       </c>
@@ -3429,7 +3425,7 @@
         <v>24449.704417000001</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
         <v>45722</v>
       </c>
@@ -3452,7 +3448,7 @@
         <v>26107.071897999998</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>45722</v>
       </c>
@@ -3475,7 +3471,7 @@
         <v>26413.639303700002</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>45722</v>
       </c>
@@ -3498,7 +3494,7 @@
         <v>25789.644590100001</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>45722</v>
       </c>
@@ -3521,7 +3517,7 @@
         <v>25946.229788299999</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
         <v>45722</v>
       </c>
@@ -3544,7 +3540,7 @@
         <v>25073.556841599999</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>45722</v>
       </c>
@@ -3567,7 +3563,7 @@
         <v>24474.246406800001</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
         <v>45722</v>
       </c>
@@ -3590,7 +3586,7 @@
         <v>23557.768391500002</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>45722</v>
       </c>
@@ -3613,7 +3609,7 @@
         <v>23554.621219000001</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>45722</v>
       </c>
@@ -3636,7 +3632,7 @@
         <v>24222.816578999998</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>45722</v>
       </c>
@@ -3659,7 +3655,7 @@
         <v>24396.411068000001</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
         <v>45722</v>
       </c>
@@ -3682,7 +3678,7 @@
         <v>25685.886132</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>45722</v>
       </c>
@@ -3705,7 +3701,7 @@
         <v>26587.314818999999</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
         <v>45722</v>
       </c>
@@ -3728,7 +3724,7 @@
         <v>26400.814028000001</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>45722</v>
       </c>
@@ -3751,7 +3747,7 @@
         <v>25987.254401999999</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
         <v>45722</v>
       </c>
@@ -3774,7 +3770,7 @@
         <v>25344.102137000002</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>45722</v>
       </c>
@@ -3797,7 +3793,7 @@
         <v>24282.407654999999</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
         <v>45722</v>
       </c>
@@ -3820,7 +3816,7 @@
         <v>23096.750646</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>45723</v>
       </c>
@@ -3843,7 +3839,7 @@
         <v>22406.978284999899</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
         <v>45723</v>
       </c>
@@ -3866,7 +3862,7 @@
         <v>21838.6724919999</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>45723</v>
       </c>
@@ -3889,7 +3885,7 @@
         <v>21280.009382</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
         <v>45723</v>
       </c>
@@ -3912,7 +3908,7 @@
         <v>20879.4581049999</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>45723</v>
       </c>
@@ -3935,7 +3931,7 @@
         <v>21381.865688999998</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
         <v>45723</v>
       </c>
@@ -3958,7 +3954,7 @@
         <v>23010.047524000001</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>45723</v>
       </c>
@@ -3981,7 +3977,7 @@
         <v>24679.028620999899</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
         <v>45723</v>
       </c>
@@ -4004,7 +4000,7 @@
         <v>24875.566116999998</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>45723</v>
       </c>
@@ -4027,7 +4023,7 @@
         <v>24108.324233399999</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
         <v>45723</v>
       </c>
@@ -4050,7 +4046,7 @@
         <v>23404.564532</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>45723</v>
       </c>
@@ -4073,7 +4069,7 @@
         <v>22153.940745</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
         <v>45723</v>
       </c>
@@ -4096,7 +4092,7 @@
         <v>22633.711704000001</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
         <v>45723</v>
       </c>
@@ -4119,7 +4115,7 @@
         <v>22785.804049999999</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
         <v>45723</v>
       </c>
@@ -4142,7 +4138,7 @@
         <v>21959.357338000002</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
         <v>45723</v>
       </c>
@@ -4165,7 +4161,7 @@
         <v>21680.625276999999</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
         <v>45723</v>
       </c>
@@ -4188,7 +4184,7 @@
         <v>20295.162844999999</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>45723</v>
       </c>
@@ -4211,7 +4207,7 @@
         <v>21082.401553</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="3">
         <v>45723</v>
       </c>
@@ -4234,7 +4230,7 @@
         <v>23629.950035000002</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
         <v>45723</v>
       </c>
@@ -4257,7 +4253,7 @@
         <v>25396.560881000001</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
         <v>45723</v>
       </c>
@@ -4280,7 +4276,7 @@
         <v>25348.071797000001</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
         <v>45723</v>
       </c>
@@ -4303,7 +4299,7 @@
         <v>24795.862615999999</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="3">
         <v>45723</v>
       </c>
@@ -4326,7 +4322,7 @@
         <v>24559.538630999999</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
         <v>45723</v>
       </c>
@@ -4349,7 +4345,7 @@
         <v>23641.995625999902</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
         <v>45723</v>
       </c>
@@ -4372,7 +4368,7 @@
         <v>22417.3829679999</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
         <v>45724</v>
       </c>
@@ -4395,7 +4391,7 @@
         <v>22087.816716000001</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="3">
         <v>45724</v>
       </c>
@@ -4418,7 +4414,7 @@
         <v>21454.475709999999</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
         <v>45724</v>
       </c>
@@ -4441,7 +4437,7 @@
         <v>20726.265261</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="3">
         <v>45724</v>
       </c>
@@ -4464,7 +4460,7 @@
         <v>20507.062683</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>45724</v>
       </c>
@@ -4487,7 +4483,7 @@
         <v>20531.589086</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
         <v>45724</v>
       </c>
@@ -4510,7 +4506,7 @@
         <v>21278.290019</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>45724</v>
       </c>
@@ -4533,7 +4529,7 @@
         <v>21772.015356</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
         <v>45724</v>
       </c>
@@ -4556,7 +4552,7 @@
         <v>21978.724472999998</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>45724</v>
       </c>
@@ -4579,7 +4575,7 @@
         <v>21820.922737999899</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>45724</v>
       </c>
@@ -4602,7 +4598,7 @@
         <v>21106.5587786</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>45724</v>
       </c>
@@ -4625,7 +4621,7 @@
         <v>19398.141151700002</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="3">
         <v>45724</v>
       </c>
@@ -4648,7 +4644,7 @@
         <v>18874.396316400002</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
         <v>45724</v>
       </c>
@@ -4671,7 +4667,7 @@
         <v>17981.9924197</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
         <v>45724</v>
       </c>
@@ -4694,7 +4690,7 @@
         <v>17038.063995999899</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
         <v>45724</v>
       </c>
@@ -4717,7 +4713,7 @@
         <v>16469.018208000001</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
         <v>45724</v>
       </c>
@@ -4740,7 +4736,7 @@
         <v>17424.717965</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
         <v>45724</v>
       </c>
@@ -4763,7 +4759,7 @@
         <v>18920.3600276</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="3">
         <v>45724</v>
       </c>
@@ -4786,7 +4782,7 @@
         <v>21936.016866999998</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
         <v>45724</v>
       </c>
@@ -4809,7 +4805,7 @@
         <v>23737.759060999899</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="3">
         <v>45724</v>
       </c>
@@ -4832,7 +4828,7 @@
         <v>23781.779869000002</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
         <v>45724</v>
       </c>
@@ -4855,7 +4851,7 @@
         <v>23460.7641</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="3">
         <v>45724</v>
       </c>
@@ -4878,7 +4874,7 @@
         <v>23031.411057000001</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
         <v>45724</v>
       </c>
@@ -4901,7 +4897,7 @@
         <v>22160.186989999998</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="3">
         <v>45724</v>
       </c>
@@ -4924,7 +4920,7 @@
         <v>21202.419825000001</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
         <v>45725</v>
       </c>
@@ -4947,7 +4943,7 @@
         <v>21061.132309000001</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
         <v>45725</v>
       </c>
@@ -4970,7 +4966,7 @@
         <v>20541.222076999999</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
         <v>45725</v>
       </c>
@@ -4993,7 +4989,7 @@
         <v>20110.532574999899</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
         <v>45725</v>
       </c>
@@ -5016,7 +5012,7 @@
         <v>19942.1825509999</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
         <v>45725</v>
       </c>
@@ -5039,7 +5035,7 @@
         <v>20260.932860000001</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
         <v>45725</v>
       </c>
@@ -5062,7 +5058,7 @@
         <v>20788.092495999899</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
         <v>45725</v>
       </c>
@@ -5085,7 +5081,7 @@
         <v>21286.622966999999</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
         <v>45725</v>
       </c>
@@ -5108,7 +5104,7 @@
         <v>21837.341912999898</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
         <v>45725</v>
       </c>
@@ -5131,7 +5127,7 @@
         <v>21771.0071971</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
         <v>45725</v>
       </c>
@@ -5154,7 +5150,7 @@
         <v>20402.821945200001</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
         <v>45725</v>
       </c>
@@ -5177,7 +5173,7 @@
         <v>19134.7738316</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
         <v>45725</v>
       </c>
@@ -5200,7 +5196,7 @@
         <v>17884.2802339999</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
         <v>45725</v>
       </c>
@@ -5223,7 +5219,7 @@
         <v>16636.977108999999</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
         <v>45725</v>
       </c>
@@ -5246,7 +5242,7 @@
         <v>16163.865218200001</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
         <v>45725</v>
       </c>
@@ -5269,7 +5265,7 @@
         <v>16137.631532199999</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
         <v>45725</v>
       </c>
@@ -5292,7 +5288,7 @@
         <v>16662.06089733</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
         <v>45725</v>
       </c>
@@ -5315,7 +5311,7 @@
         <v>18899.112874400002</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
         <v>45725</v>
       </c>
@@ -5338,7 +5334,7 @@
         <v>21972.219594999999</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
         <v>45725</v>
       </c>
@@ -5361,7 +5357,7 @@
         <v>23803.0055179999</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
         <v>45725</v>
       </c>
@@ -5384,7 +5380,7 @@
         <v>23766.056076000001</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
         <v>45725</v>
       </c>
@@ -5407,7 +5403,7 @@
         <v>23451.473600000001</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
         <v>45725</v>
       </c>
@@ -5430,7 +5426,7 @@
         <v>22407.473496999999</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
         <v>45725</v>
       </c>
@@ -5453,7 +5449,7 @@
         <v>21290.559937999999</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="3">
         <v>45726</v>
       </c>
@@ -5476,7 +5472,7 @@
         <v>21114.092219999999</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
         <v>45726</v>
       </c>
@@ -5499,7 +5495,7 @@
         <v>20577.373434000001</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="3">
         <v>45726</v>
       </c>
@@ -5522,7 +5518,7 @@
         <v>20269.264155999899</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="3">
         <v>45726</v>
       </c>
@@ -5545,7 +5541,7 @@
         <v>20074.392528</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="3">
         <v>45726</v>
       </c>
@@ -5568,7 +5564,7 @@
         <v>20433.663228000001</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
         <v>45726</v>
       </c>
@@ -5591,7 +5587,7 @@
         <v>21961.693735000001</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="3">
         <v>45726</v>
       </c>
@@ -5614,7 +5610,7 @@
         <v>24041.940580999999</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
         <v>45726</v>
       </c>
@@ -5637,7 +5633,7 @@
         <v>25459.905004</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="3">
         <v>45726</v>
       </c>
@@ -5660,7 +5656,7 @@
         <v>26284.900517999999</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
         <v>45726</v>
       </c>
@@ -5683,7 +5679,7 @@
         <v>26071.479052999999</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
         <v>45726</v>
       </c>
@@ -5706,7 +5702,7 @@
         <v>24709.506246000001</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
         <v>45726</v>
       </c>
@@ -5729,7 +5725,7 @@
         <v>23106.479902999999</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="3">
         <v>45726</v>
       </c>
@@ -5752,7 +5748,7 @@
         <v>21624.678166000002</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="3">
         <v>45726</v>
       </c>
@@ -5775,7 +5771,7 @@
         <v>20368.757798999999</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="3">
         <v>45726</v>
       </c>
@@ -5798,7 +5794,7 @@
         <v>20183.357174000001</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
         <v>45726</v>
       </c>
@@ -5821,7 +5817,7 @@
         <v>20118.260966999998</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="3">
         <v>45726</v>
       </c>
@@ -5844,7 +5840,7 @@
         <v>20717.7726469999</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
         <v>45726</v>
       </c>
@@ -5867,7 +5863,7 @@
         <v>21764.631053000001</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="3">
         <v>45726</v>
       </c>
@@ -5890,7 +5886,7 @@
         <v>23718.792262999999</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
         <v>45726</v>
       </c>
@@ -5913,7 +5909,7 @@
         <v>25330.872646</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="3">
         <v>45726</v>
       </c>
@@ -5936,7 +5932,7 @@
         <v>24983.727035</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
         <v>45726</v>
       </c>
@@ -5959,7 +5955,7 @@
         <v>24291.432118999899</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
         <v>45726</v>
       </c>
@@ -5982,7 +5978,7 @@
         <v>23045.990827000001</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="3">
         <v>45726</v>
       </c>
@@ -6005,7 +6001,7 @@
         <v>21595.493602999999</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="3">
         <v>45727</v>
       </c>
@@ -6028,7 +6024,7 @@
         <v>21626.353052999999</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="3">
         <v>45727</v>
       </c>
@@ -6051,7 +6047,7 @@
         <v>20641.900319</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="3">
         <v>45727</v>
       </c>
@@ -6074,7 +6070,7 @@
         <v>20401.919703</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="3">
         <v>45727</v>
       </c>
@@ -6097,7 +6093,7 @@
         <v>20173.750894999899</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="3">
         <v>45727</v>
       </c>
@@ -6120,7 +6116,7 @@
         <v>20240.529476</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="3">
         <v>45727</v>
       </c>
@@ -6143,7 +6139,7 @@
         <v>21275.078336999999</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="3">
         <v>45727</v>
       </c>
@@ -6166,7 +6162,7 @@
         <v>23598.207941000001</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="3">
         <v>45727</v>
       </c>
@@ -6189,7 +6185,7 @@
         <v>25424.666142999999</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="3">
         <v>45727</v>
       </c>
@@ -6212,7 +6208,7 @@
         <v>25079.2400429999</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="3">
         <v>45727</v>
       </c>
@@ -6235,7 +6231,7 @@
         <v>23996.858143000001</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="3">
         <v>45727</v>
       </c>
@@ -6258,7 +6254,7 @@
         <v>22891.399186999999</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="3">
         <v>45727</v>
       </c>
@@ -6281,7 +6277,7 @@
         <v>23096.781953999998</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="3">
         <v>45727</v>
       </c>
@@ -6304,7 +6300,7 @@
         <v>22768.199452000001</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="3">
         <v>45727</v>
       </c>
@@ -6327,7 +6323,7 @@
         <v>23047.321236</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="3">
         <v>45727</v>
       </c>
@@ -6350,7 +6346,7 @@
         <v>21985.371807</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="3">
         <v>45727</v>
       </c>
@@ -6373,7 +6369,7 @@
         <v>22587.121832000001</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="3">
         <v>45727</v>
       </c>
@@ -6396,7 +6392,7 @@
         <v>22858.135713</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="3">
         <v>45727</v>
       </c>
@@ -6419,7 +6415,7 @@
         <v>22867.8723939999</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="3">
         <v>45727</v>
       </c>
@@ -6442,7 +6438,7 @@
         <v>24340.279619999899</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="3">
         <v>45727</v>
       </c>
@@ -6465,7 +6461,7 @@
         <v>25773.373836999999</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="3">
         <v>45727</v>
       </c>
@@ -6488,7 +6484,7 @@
         <v>25406.814659</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="3">
         <v>45727</v>
       </c>
@@ -6511,7 +6507,7 @@
         <v>24787.295977000002</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="3">
         <v>45727</v>
       </c>
@@ -6534,7 +6530,7 @@
         <v>23411.081053999998</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="3">
         <v>45727</v>
       </c>
@@ -6557,7 +6553,7 @@
         <v>22169.110588</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="3">
         <v>45728</v>
       </c>
@@ -6580,7 +6576,7 @@
         <v>21711.800732</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="3">
         <v>45728</v>
       </c>
@@ -6603,7 +6599,7 @@
         <v>21195.527314999999</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="3">
         <v>45728</v>
       </c>
@@ -6626,7 +6622,7 @@
         <v>21024.617539999999</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="3">
         <v>45728</v>
       </c>
@@ -6649,7 +6645,7 @@
         <v>20687.031975999998</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="3">
         <v>45728</v>
       </c>
@@ -6672,7 +6668,7 @@
         <v>20486.0170159999</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="3">
         <v>45728</v>
       </c>
@@ -6695,7 +6691,7 @@
         <v>21301.261666999999</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="3">
         <v>45728</v>
       </c>
@@ -6718,7 +6714,7 @@
         <v>23155.510618</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="3">
         <v>45728</v>
       </c>
@@ -6741,7 +6737,7 @@
         <v>24994.685285</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="3">
         <v>45728</v>
       </c>
@@ -6764,7 +6760,7 @@
         <v>26129.562287000001</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="3">
         <v>45728</v>
       </c>
@@ -6787,7 +6783,7 @@
         <v>26249.301034999899</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="3">
         <v>45728</v>
       </c>
@@ -6810,7 +6806,7 @@
         <v>26687.303257</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="3">
         <v>45728</v>
       </c>
@@ -6833,7 +6829,7 @@
         <v>26397.976515999999</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="3">
         <v>45728</v>
       </c>
@@ -6856,7 +6852,7 @@
         <v>25349.561728000001</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="3">
         <v>45728</v>
       </c>
@@ -6879,7 +6875,7 @@
         <v>24277.840669000001</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="3">
         <v>45728</v>
       </c>
@@ -6902,7 +6898,7 @@
         <v>24890.106445000001</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="3">
         <v>45728</v>
       </c>
@@ -6925,7 +6921,7 @@
         <v>24464.779730999999</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="3">
         <v>45728</v>
       </c>
@@ -6948,7 +6944,7 @@
         <v>24445.2904529999</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="3">
         <v>45728</v>
       </c>
@@ -6971,7 +6967,7 @@
         <v>24227.312894999999</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="3">
         <v>45728</v>
       </c>
@@ -6994,7 +6990,7 @@
         <v>25151.492747</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="3">
         <v>45728</v>
       </c>
@@ -7017,7 +7013,7 @@
         <v>26273.004410000001</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="3">
         <v>45728</v>
       </c>
@@ -7040,7 +7036,7 @@
         <v>25960.969568</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="3">
         <v>45728</v>
       </c>
@@ -7063,7 +7059,7 @@
         <v>25075.093022999899</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="3">
         <v>45728</v>
       </c>
@@ -7086,7 +7082,7 @@
         <v>23886.309517000002</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="3">
         <v>45728</v>
       </c>
@@ -7109,7 +7105,7 @@
         <v>22442.091635000001</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="3">
         <v>45729</v>
       </c>
@@ -7132,7 +7128,7 @@
         <v>22237.4473379999</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="3">
         <v>45729</v>
       </c>
@@ -7155,7 +7151,7 @@
         <v>22066.412973999999</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="3">
         <v>45729</v>
       </c>
@@ -7178,7 +7174,7 @@
         <v>21402.396313000001</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="3">
         <v>45729</v>
       </c>
@@ -7201,7 +7197,7 @@
         <v>21532.913236</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="3">
         <v>45729</v>
       </c>
@@ -7224,7 +7220,7 @@
         <v>20953.941468999899</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="3">
         <v>45729</v>
       </c>
@@ -7247,7 +7243,7 @@
         <v>22081.696089000001</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="3">
         <v>45729</v>
       </c>
@@ -7270,7 +7266,7 @@
         <v>24048.732769999999</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="3">
         <v>45729</v>
       </c>
@@ -7293,7 +7289,7 @@
         <v>25850.142365</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="3">
         <v>45729</v>
       </c>
@@ -7316,7 +7312,7 @@
         <v>26468.562645000002</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="3">
         <v>45729</v>
       </c>
@@ -7339,7 +7335,7 @@
         <v>26146.285381000002</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="3">
         <v>45729</v>
       </c>
@@ -7362,7 +7358,7 @@
         <v>25447.181363</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="3">
         <v>45729</v>
       </c>
@@ -7385,7 +7381,7 @@
         <v>25260.737733000002</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="3">
         <v>45729</v>
       </c>
@@ -7408,7 +7404,7 @@
         <v>24539.122928000001</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="3">
         <v>45729</v>
       </c>
@@ -7431,7 +7427,7 @@
         <v>23496.865403</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="3">
         <v>45729</v>
       </c>
@@ -7454,7 +7450,7 @@
         <v>23777.2871969999</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="3">
         <v>45729</v>
       </c>
@@ -7477,7 +7473,7 @@
         <v>22999.888936399999</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="3">
         <v>45729</v>
       </c>
@@ -7500,7 +7496,7 @@
         <v>22270.620626100001</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="3">
         <v>45729</v>
       </c>
@@ -7523,7 +7519,7 @@
         <v>22856.398487999999</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="3">
         <v>45729</v>
       </c>
@@ -7546,7 +7542,7 @@
         <v>24726.987331</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="3">
         <v>45729</v>
       </c>
@@ -7569,7 +7565,7 @@
         <v>26516.654467</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="3">
         <v>45729</v>
       </c>
@@ -7592,7 +7588,7 @@
         <v>26452.011276000001</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="3">
         <v>45729</v>
       </c>
@@ -7615,7 +7611,7 @@
         <v>26001.465465000001</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="3">
         <v>45729</v>
       </c>
@@ -7638,7 +7634,7 @@
         <v>24594.141722</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="3">
         <v>45729</v>
       </c>
@@ -7661,7 +7657,7 @@
         <v>22924.176242000001</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="3">
         <v>45730</v>
       </c>
@@ -7684,7 +7680,7 @@
         <v>22690.955458</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="3">
         <v>45730</v>
       </c>
@@ -7707,7 +7703,7 @@
         <v>22023.829425</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="3">
         <v>45730</v>
       </c>
@@ -7730,7 +7726,7 @@
         <v>21745.320419</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="3">
         <v>45730</v>
       </c>
@@ -7753,7 +7749,7 @@
         <v>21381.771633</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="3">
         <v>45730</v>
       </c>
@@ -7776,7 +7772,7 @@
         <v>21443.159715000002</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="3">
         <v>45730</v>
       </c>
@@ -7799,7 +7795,7 @@
         <v>22577.489128000001</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="3">
         <v>45730</v>
       </c>
@@ -7822,7 +7818,7 @@
         <v>24716.328025999999</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="3">
         <v>45730</v>
       </c>
@@ -7845,7 +7841,7 @@
         <v>26550.106911999999</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="3">
         <v>45730</v>
       </c>
@@ -7868,7 +7864,7 @@
         <v>27568.457641999899</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="3">
         <v>45730</v>
       </c>
@@ -7891,7 +7887,7 @@
         <v>27704.122802000002</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="3">
         <v>45730</v>
       </c>
@@ -7914,7 +7910,7 @@
         <v>28127.034768000001</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="3">
         <v>45730</v>
       </c>
@@ -7937,7 +7933,7 @@
         <v>27429.828745999999</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="3">
         <v>45730</v>
       </c>
@@ -7960,7 +7956,7 @@
         <v>26100.577889</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="3">
         <v>45730</v>
       </c>
@@ -7983,7 +7979,7 @@
         <v>27010.426820999899</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="3">
         <v>45730</v>
       </c>
@@ -8006,7 +8002,7 @@
         <v>26908.737187999999</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="3">
         <v>45730</v>
       </c>
@@ -8029,7 +8025,7 @@
         <v>26128.238322000001</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="3">
         <v>45730</v>
       </c>
@@ -8052,7 +8048,7 @@
         <v>25088.47738</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="3">
         <v>45730</v>
       </c>
@@ -8075,7 +8071,7 @@
         <v>24730.048929</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="3">
         <v>45730</v>
       </c>
@@ -8098,7 +8094,7 @@
         <v>25434.914360999999</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="3">
         <v>45730</v>
       </c>
@@ -8121,7 +8117,7 @@
         <v>26406.634343000002</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="3">
         <v>45730</v>
       </c>
@@ -8144,7 +8140,7 @@
         <v>26129.645374</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="3">
         <v>45730</v>
       </c>
@@ -8167,7 +8163,7 @@
         <v>25561.724389999999</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="3">
         <v>45730</v>
       </c>
@@ -8190,7 +8186,7 @@
         <v>24462.317099</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="3">
         <v>45730</v>
       </c>
@@ -8213,7 +8209,7 @@
         <v>23366.420266000001</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="3">
         <v>45731</v>
       </c>
@@ -8236,7 +8232,7 @@
         <v>22946.193996999998</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="3">
         <v>45731</v>
       </c>
@@ -8259,7 +8255,7 @@
         <v>22313.413699000001</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="3">
         <v>45731</v>
       </c>
@@ -8282,7 +8278,7 @@
         <v>21419.304473</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="3">
         <v>45731</v>
       </c>
@@ -8305,7 +8301,7 @@
         <v>20977.490314999999</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="3">
         <v>45731</v>
       </c>
@@ -8328,7 +8324,7 @@
         <v>20780.122847999999</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="3">
         <v>45731</v>
       </c>
@@ -8351,7 +8347,7 @@
         <v>21361.582866999899</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" s="3">
         <v>45731</v>
       </c>
@@ -8374,7 +8370,7 @@
         <v>22384.670158000001</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="3">
         <v>45731</v>
       </c>
@@ -8397,7 +8393,7 @@
         <v>23150.996454</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="3">
         <v>45731</v>
       </c>
@@ -8420,7 +8416,7 @@
         <v>23691.599477</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="3">
         <v>45731</v>
       </c>
@@ -8443,7 +8439,7 @@
         <v>23328.755118999899</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="3">
         <v>45731</v>
       </c>
@@ -8466,7 +8462,7 @@
         <v>21552.8855081</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="3">
         <v>45731</v>
       </c>
@@ -8489,7 +8485,7 @@
         <v>20855.155740400001</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="3">
         <v>45731</v>
       </c>
@@ -8512,7 +8508,7 @@
         <v>20972.227241000001</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" s="3">
         <v>45731</v>
       </c>
@@ -8535,7 +8531,7 @@
         <v>19905.984294000002</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" s="3">
         <v>45731</v>
       </c>
@@ -8558,7 +8554,7 @@
         <v>18968.6411171</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="3">
         <v>45731</v>
       </c>
@@ -8581,7 +8577,7 @@
         <v>17867.277979999999</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" s="3">
         <v>45731</v>
       </c>
@@ -8604,7 +8600,7 @@
         <v>17771.244178000001</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" s="3">
         <v>45731</v>
       </c>
@@ -8627,7 +8623,7 @@
         <v>19201.237461000001</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="3">
         <v>45731</v>
       </c>
@@ -8650,7 +8646,7 @@
         <v>21561.546268999999</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="3">
         <v>45731</v>
       </c>
@@ -8673,7 +8669,7 @@
         <v>23363.613008</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="3">
         <v>45731</v>
       </c>
@@ -8696,7 +8692,7 @@
         <v>23486.608397</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="3">
         <v>45731</v>
       </c>
@@ -8719,7 +8715,7 @@
         <v>23334.742165</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" s="3">
         <v>45731</v>
       </c>
@@ -8742,7 +8738,7 @@
         <v>22523.064766</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" s="3">
         <v>45731</v>
       </c>
@@ -8765,7 +8761,7 @@
         <v>21773.871123000001</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="3">
         <v>45732</v>
       </c>
@@ -8788,7 +8784,7 @@
         <v>21403.7745379999</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" s="3">
         <v>45732</v>
       </c>
@@ -8811,7 +8807,7 @@
         <v>20785.185130999998</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="3">
         <v>45732</v>
       </c>
@@ -8834,7 +8830,7 @@
         <v>20092.070070000002</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="3">
         <v>45732</v>
       </c>
@@ -8857,7 +8853,7 @@
         <v>19843.869371000001</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="3">
         <v>45732</v>
       </c>
@@ -8880,7 +8876,7 @@
         <v>19593.516529</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="3">
         <v>45732</v>
       </c>
@@ -8903,7 +8899,7 @@
         <v>19991.337071999998</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" s="3">
         <v>45732</v>
       </c>
@@ -8926,7 +8922,7 @@
         <v>20807.685168</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="3">
         <v>45732</v>
       </c>
@@ -8949,7 +8945,7 @@
         <v>21097.951194000001</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" s="3">
         <v>45732</v>
       </c>
@@ -8972,7 +8968,7 @@
         <v>21985.169985</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="3">
         <v>45732</v>
       </c>
@@ -8995,7 +8991,7 @@
         <v>22355.069406999999</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="3">
         <v>45732</v>
       </c>
@@ -9018,7 +9014,7 @@
         <v>21009.8899209999</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" s="3">
         <v>45732</v>
       </c>
@@ -9041,7 +9037,7 @@
         <v>20863.465034000001</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="3">
         <v>45732</v>
       </c>
@@ -9064,7 +9060,7 @@
         <v>20238.285524999999</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" s="3">
         <v>45732</v>
       </c>
@@ -9087,7 +9083,7 @@
         <v>18965.695803999999</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="3">
         <v>45732</v>
       </c>
@@ -9110,7 +9106,7 @@
         <v>18960.84474</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" s="3">
         <v>45732</v>
       </c>
@@ -9133,7 +9129,7 @@
         <v>18777.360808699999</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" s="3">
         <v>45732</v>
       </c>
@@ -9156,7 +9152,7 @@
         <v>19138.057706600001</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="3">
         <v>45732</v>
       </c>
@@ -9179,7 +9175,7 @@
         <v>20382.1362989999</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="3">
         <v>45732</v>
       </c>
@@ -9202,7 +9198,7 @@
         <v>22207.359186999998</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" s="3">
         <v>45732</v>
       </c>
@@ -9225,7 +9221,7 @@
         <v>23900.062881999998</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="3">
         <v>45732</v>
       </c>
@@ -9248,7 +9244,7 @@
         <v>23703.383739000001</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" s="3">
         <v>45732</v>
       </c>
@@ -9271,7 +9267,7 @@
         <v>23265.541374</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" s="3">
         <v>45732</v>
       </c>
@@ -9294,7 +9290,7 @@
         <v>22105.1646579999</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="3">
         <v>45732</v>
       </c>
@@ -9317,7 +9313,7 @@
         <v>20897.602329000001</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="3">
         <v>45733</v>
       </c>
@@ -9340,7 +9336,7 @@
         <v>20846.571992000001</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="3">
         <v>45733</v>
       </c>
@@ -9363,7 +9359,7 @@
         <v>20287.073061999999</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="3">
         <v>45733</v>
       </c>
@@ -9386,7 +9382,7 @@
         <v>19930.010143</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="3">
         <v>45733</v>
       </c>
@@ -9409,7 +9405,7 @@
         <v>20167.2749679999</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="3">
         <v>45733</v>
       </c>
@@ -9432,7 +9428,7 @@
         <v>20139.260235999998</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" s="3">
         <v>45733</v>
       </c>
@@ -9455,7 +9451,7 @@
         <v>21292.687540999999</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="3">
         <v>45733</v>
       </c>
@@ -9478,7 +9474,7 @@
         <v>23253.607723999899</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" s="3">
         <v>45733</v>
       </c>
@@ -9501,7 +9497,7 @@
         <v>24834.176899999999</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" s="3">
         <v>45733</v>
       </c>
@@ -9524,7 +9520,7 @@
         <v>24911.968745999999</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" s="3">
         <v>45733</v>
       </c>
@@ -9547,7 +9543,7 @@
         <v>24743.384993</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" s="3">
         <v>45733</v>
       </c>
@@ -9570,7 +9566,7 @@
         <v>24665.342551999998</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" s="3">
         <v>45733</v>
       </c>
@@ -9593,7 +9589,7 @@
         <v>25271.589779999998</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" s="3">
         <v>45733</v>
       </c>
@@ -9616,7 +9612,7 @@
         <v>24340.653911000001</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" s="3">
         <v>45733</v>
       </c>
@@ -9639,7 +9635,7 @@
         <v>24230.136686999998</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" s="3">
         <v>45733</v>
       </c>
@@ -9662,7 +9658,7 @@
         <v>23963.058381999999</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="3">
         <v>45733</v>
       </c>
@@ -9685,7 +9681,7 @@
         <v>22879.526677999998</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" s="3">
         <v>45733</v>
       </c>
@@ -9708,7 +9704,7 @@
         <v>22994.817809</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="3">
         <v>45733</v>
       </c>
@@ -9731,7 +9727,7 @@
         <v>23938.887124000001</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" s="3">
         <v>45733</v>
       </c>
@@ -9754,7 +9750,7 @@
         <v>24681.792119000002</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" s="3">
         <v>45733</v>
       </c>
@@ -9777,7 +9773,7 @@
         <v>26033.245096999999</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" s="3">
         <v>45733</v>
       </c>
@@ -9800,7 +9796,7 @@
         <v>25803.418546000001</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" s="3">
         <v>45733</v>
       </c>
@@ -9823,7 +9819,7 @@
         <v>25136.432961999999</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="3">
         <v>45733</v>
       </c>
@@ -9846,7 +9842,7 @@
         <v>23873.8922409999</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" s="3">
         <v>45733</v>
       </c>
@@ -9869,7 +9865,7 @@
         <v>22651.199272999998</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" s="3">
         <v>45734</v>
       </c>
@@ -9892,7 +9888,7 @@
         <v>22069.125080000002</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" s="3">
         <v>45734</v>
       </c>
@@ -9915,7 +9911,7 @@
         <v>21538.270335000001</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="3">
         <v>45734</v>
       </c>
@@ -9938,7 +9934,7 @@
         <v>21027.689855000001</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412" s="3">
         <v>45734</v>
       </c>
@@ -9961,7 +9957,7 @@
         <v>20783.056081999999</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" s="3">
         <v>45734</v>
       </c>
@@ -9984,7 +9980,7 @@
         <v>20989.566449999998</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" s="3">
         <v>45734</v>
       </c>
@@ -10007,7 +10003,7 @@
         <v>22449.167538000002</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" s="3">
         <v>45734</v>
       </c>
@@ -10030,7 +10026,7 @@
         <v>24741.8371669999</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="3">
         <v>45734</v>
       </c>
@@ -10053,7 +10049,7 @@
         <v>26353.294116999899</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="3">
         <v>45734</v>
       </c>
@@ -10076,7 +10072,7 @@
         <v>25972.879960999999</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="3">
         <v>45734</v>
       </c>
@@ -10099,7 +10095,7 @@
         <v>25009.906922999999</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="3">
         <v>45734</v>
       </c>
@@ -10122,7 +10118,7 @@
         <v>22534.474491999899</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="3">
         <v>45734</v>
       </c>
@@ -10145,7 +10141,7 @@
         <v>21794.731715999998</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="3">
         <v>45734</v>
       </c>
@@ -10168,7 +10164,7 @@
         <v>21129.956434</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="3">
         <v>45734</v>
       </c>
@@ -10191,7 +10187,7 @@
         <v>20043.578487999999</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="3">
         <v>45734</v>
       </c>
@@ -10214,7 +10210,7 @@
         <v>19590.385127500002</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="3">
         <v>45734</v>
       </c>
@@ -10237,7 +10233,7 @@
         <v>19418.455904999999</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="3">
         <v>45734</v>
       </c>
@@ -10260,7 +10256,7 @@
         <v>19054.794929</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="3">
         <v>45734</v>
       </c>
@@ -10283,7 +10279,7 @@
         <v>20871.435301400001</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="3">
         <v>45734</v>
       </c>
@@ -10306,7 +10302,7 @@
         <v>23235.588079000001</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="3">
         <v>45734</v>
       </c>
@@ -10329,7 +10325,7 @@
         <v>25179.5168439999</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="3">
         <v>45734</v>
       </c>
@@ -10352,7 +10348,7 @@
         <v>25056.418462000001</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="3">
         <v>45734</v>
       </c>
@@ -10375,7 +10371,7 @@
         <v>24526.4974359999</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="3">
         <v>45734</v>
       </c>
@@ -10398,7 +10394,7 @@
         <v>23273.227983000001</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="3">
         <v>45734</v>
       </c>
@@ -10421,7 +10417,7 @@
         <v>21906.2031409999</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="3">
         <v>45735</v>
       </c>
@@ -10444,7 +10440,7 @@
         <v>21718.224088999999</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="3">
         <v>45735</v>
       </c>
@@ -10467,7 +10463,7 @@
         <v>21021.820947</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="3">
         <v>45735</v>
       </c>
@@ -10490,7 +10486,7 @@
         <v>20385.207601999999</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="3">
         <v>45735</v>
       </c>
@@ -10513,7 +10509,7 @@
         <v>20508.590435999999</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="3">
         <v>45735</v>
       </c>
@@ -10536,7 +10532,7 @@
         <v>21094.400651</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="3">
         <v>45735</v>
       </c>
@@ -10559,7 +10555,7 @@
         <v>22748.286699</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="3">
         <v>45735</v>
       </c>
@@ -10582,7 +10578,7 @@
         <v>24908.564166</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="3">
         <v>45735</v>
       </c>
@@ -10605,7 +10601,7 @@
         <v>26553.561516999998</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="3">
         <v>45735</v>
       </c>
@@ -10628,7 +10624,7 @@
         <v>26591.493460999998</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="3">
         <v>45735</v>
       </c>
@@ -10651,7 +10647,7 @@
         <v>24662.778521</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="3">
         <v>45735</v>
       </c>
@@ -10674,7 +10670,7 @@
         <v>23634.542251999999</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="3">
         <v>45735</v>
       </c>
@@ -10697,7 +10693,7 @@
         <v>22962.168664000001</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="3">
         <v>45735</v>
       </c>
@@ -10720,7 +10716,7 @@
         <v>22371.681871000001</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="3">
         <v>45735</v>
       </c>
@@ -10743,7 +10739,7 @@
         <v>21927.874272199999</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="3">
         <v>45735</v>
       </c>
@@ -10766,7 +10762,7 @@
         <v>21290.365031199999</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="3">
         <v>45735</v>
       </c>
@@ -10789,7 +10785,7 @@
         <v>20547.931911</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" s="3">
         <v>45735</v>
       </c>
@@ -10812,7 +10808,7 @@
         <v>21160.364172000001</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" s="3">
         <v>45735</v>
       </c>
@@ -10835,7 +10831,7 @@
         <v>22245.180817</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" s="3">
         <v>45735</v>
       </c>
@@ -10858,7 +10854,7 @@
         <v>24057.941511000001</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452" s="3">
         <v>45735</v>
       </c>
@@ -10881,7 +10877,7 @@
         <v>25336.054289</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453" s="3">
         <v>45735</v>
       </c>
@@ -10904,7 +10900,7 @@
         <v>25172.430490999999</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" s="3">
         <v>45735</v>
       </c>
@@ -10927,7 +10923,7 @@
         <v>24744.176883</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455" s="3">
         <v>45735</v>
       </c>
@@ -10950,7 +10946,7 @@
         <v>23280.669355999999</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" s="3">
         <v>45735</v>
       </c>
@@ -10973,7 +10969,7 @@
         <v>22156.768722000001</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" s="3">
         <v>45736</v>
       </c>
@@ -10996,7 +10992,7 @@
         <v>21705.226741999999</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458" s="3">
         <v>45736</v>
       </c>
@@ -11019,7 +11015,7 @@
         <v>21065.368251</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459" s="3">
         <v>45736</v>
       </c>
@@ -11042,7 +11038,7 @@
         <v>20666.509674000001</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460" s="3">
         <v>45736</v>
       </c>
@@ -11065,7 +11061,7 @@
         <v>20837.915147</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461" s="3">
         <v>45736</v>
       </c>
@@ -11088,7 +11084,7 @@
         <v>20781.060431999998</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462" s="3">
         <v>45736</v>
       </c>
@@ -11111,7 +11107,7 @@
         <v>21899.914783</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" s="3">
         <v>45736</v>
       </c>
@@ -11134,7 +11130,7 @@
         <v>24057.142658000001</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" s="3">
         <v>45736</v>
       </c>
@@ -11157,7 +11153,7 @@
         <v>25718.022626999998</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465" s="3">
         <v>45736</v>
       </c>
@@ -11180,7 +11176,7 @@
         <v>25694.198101999998</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466" s="3">
         <v>45736</v>
       </c>
@@ -11203,7 +11199,7 @@
         <v>25166.662920499999</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467" s="3">
         <v>45736</v>
       </c>
@@ -11226,7 +11222,7 @@
         <v>23541.463513229999</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468" s="3">
         <v>45736</v>
       </c>
@@ -11249,7 +11245,7 @@
         <v>22061.558344599998</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" s="3">
         <v>45736</v>
       </c>
@@ -11272,7 +11268,7 @@
         <v>21543.173790199999</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" s="3">
         <v>45736</v>
       </c>
@@ -11295,7 +11291,7 @@
         <v>20698.866682</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" s="3">
         <v>45736</v>
       </c>
@@ -11318,7 +11314,7 @@
         <v>19258.280742999999</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472" s="3">
         <v>45736</v>
       </c>
@@ -11341,7 +11337,7 @@
         <v>19795.503567</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" s="3">
         <v>45736</v>
       </c>
@@ -11364,7 +11360,7 @@
         <v>19757.098323300001</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474" s="3">
         <v>45736</v>
       </c>
@@ -11387,7 +11383,7 @@
         <v>21326.587017899899</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475" s="3">
         <v>45736</v>
       </c>
@@ -11410,7 +11406,7 @@
         <v>23338.3060459999</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476" s="3">
         <v>45736</v>
       </c>
@@ -11433,7 +11429,7 @@
         <v>25138.541303000002</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" s="3">
         <v>45736</v>
       </c>
@@ -11456,7 +11452,7 @@
         <v>25090.1286469999</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478" s="3">
         <v>45736</v>
       </c>
@@ -11479,7 +11475,7 @@
         <v>24407.432681999999</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" s="3">
         <v>45736</v>
       </c>
@@ -11502,7 +11498,7 @@
         <v>23205.731774</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" s="3">
         <v>45736</v>
       </c>
@@ -11525,7 +11521,7 @@
         <v>21757.694112000001</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" s="3">
         <v>45737</v>
       </c>
@@ -11548,7 +11544,7 @@
         <v>21445.343021000001</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" s="3">
         <v>45737</v>
       </c>
@@ -11571,7 +11567,7 @@
         <v>20940.476837999999</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="3">
         <v>45737</v>
       </c>
@@ -11594,7 +11590,7 @@
         <v>20627.754868</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" s="3">
         <v>45737</v>
       </c>
@@ -11617,7 +11613,7 @@
         <v>20302.310906999999</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="3">
         <v>45737</v>
       </c>
@@ -11640,7 +11636,7 @@
         <v>20496.07444</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" s="3">
         <v>45737</v>
       </c>
@@ -11663,7 +11659,7 @@
         <v>21832.616275</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A487" s="3">
         <v>45737</v>
       </c>
@@ -11686,7 +11682,7 @@
         <v>23917.712946</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" s="3">
         <v>45737</v>
       </c>
@@ -11709,7 +11705,7 @@
         <v>25239.282725000001</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="3">
         <v>45737</v>
       </c>
@@ -11732,7 +11728,7 @@
         <v>25076.784060999998</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490" s="3">
         <v>45737</v>
       </c>
@@ -11755,7 +11751,7 @@
         <v>23830.097277999899</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="3">
         <v>45737</v>
       </c>
@@ -11778,7 +11774,7 @@
         <v>22770.155025</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="3">
         <v>45737</v>
       </c>
@@ -11801,7 +11797,7 @@
         <v>21528.6325965</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="3">
         <v>45737</v>
       </c>
@@ -11824,7 +11820,7 @@
         <v>21278.052579700001</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="3">
         <v>45737</v>
       </c>
@@ -11847,7 +11843,7 @@
         <v>21301.970988100002</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="3">
         <v>45737</v>
       </c>
@@ -11870,7 +11866,7 @@
         <v>20975.093427199899</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="3">
         <v>45737</v>
       </c>
@@ -11893,7 +11889,7 @@
         <v>20675.598283399999</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="3">
         <v>45737</v>
       </c>
@@ -11916,7 +11912,7 @@
         <v>20584.2288176</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="3">
         <v>45737</v>
       </c>
@@ -11939,7 +11935,7 @@
         <v>21381.134915499999</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="3">
         <v>45737</v>
       </c>
@@ -11962,7 +11958,7 @@
         <v>22951.5608709999</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="3">
         <v>45737</v>
       </c>
@@ -11985,7 +11981,7 @@
         <v>24366.818934999999</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="3">
         <v>45737</v>
       </c>
@@ -12008,7 +12004,7 @@
         <v>24183.440793999998</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="3">
         <v>45737</v>
       </c>
@@ -12031,7 +12027,7 @@
         <v>23756.383820999999</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="3">
         <v>45737</v>
       </c>
@@ -12054,7 +12050,7 @@
         <v>23000.410727999999</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="3">
         <v>45737</v>
       </c>
@@ -12077,7 +12073,7 @@
         <v>21955.369576999899</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="3">
         <v>45738</v>
       </c>
@@ -12100,7 +12096,7 @@
         <v>21199.123952999998</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="3">
         <v>45738</v>
       </c>
@@ -12123,7 +12119,7 @@
         <v>20581.016760999999</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="3">
         <v>45738</v>
       </c>
@@ -12146,7 +12142,7 @@
         <v>20043.292709000001</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="3">
         <v>45738</v>
       </c>
@@ -12169,7 +12165,7 @@
         <v>19593.070496</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="3">
         <v>45738</v>
       </c>
@@ -12192,7 +12188,7 @@
         <v>19610.580164999999</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="3">
         <v>45738</v>
       </c>
@@ -12215,7 +12211,7 @@
         <v>20163.474552</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="3">
         <v>45738</v>
       </c>
@@ -12238,7 +12234,7 @@
         <v>20636.374126999999</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="3">
         <v>45738</v>
       </c>
@@ -12261,7 +12257,7 @@
         <v>21167.292823</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513" s="3">
         <v>45738</v>
       </c>
@@ -12284,7 +12280,7 @@
         <v>21473.7948989</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" s="3">
         <v>45738</v>
       </c>
@@ -12307,7 +12303,7 @@
         <v>20681.262976000002</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" s="3">
         <v>45738</v>
       </c>
@@ -12330,7 +12326,7 @@
         <v>19538.612699000001</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516" s="3">
         <v>45738</v>
       </c>
@@ -12353,7 +12349,7 @@
         <v>19002.168777999999</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517" s="3">
         <v>45738</v>
       </c>
@@ -12376,7 +12372,7 @@
         <v>19194.081092699998</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518" s="3">
         <v>45738</v>
       </c>
@@ -12399,7 +12395,7 @@
         <v>19026.361100999999</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519" s="3">
         <v>45738</v>
       </c>
@@ -12422,7 +12418,7 @@
         <v>18830.305309700001</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A520" s="3">
         <v>45738</v>
       </c>
@@ -12445,7 +12441,7 @@
         <v>19078.277695000001</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A521" s="3">
         <v>45738</v>
       </c>
@@ -12468,7 +12464,7 @@
         <v>18912.969953</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A522" s="3">
         <v>45738</v>
       </c>
@@ -12491,7 +12487,7 @@
         <v>20004.557268</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A523" s="3">
         <v>45738</v>
       </c>
@@ -12514,7 +12510,7 @@
         <v>21635.534673999999</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524" s="3">
         <v>45738</v>
       </c>
@@ -12537,7 +12533,7 @@
         <v>23224.449175999998</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A525" s="3">
         <v>45738</v>
       </c>
@@ -12560,7 +12556,7 @@
         <v>23264.737002000002</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A526" s="3">
         <v>45738</v>
       </c>
@@ -12583,7 +12579,7 @@
         <v>22866.259839999999</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527" s="3">
         <v>45738</v>
       </c>
@@ -12606,7 +12602,7 @@
         <v>22085.181807000001</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A528" s="3">
         <v>45738</v>
       </c>
@@ -12629,7 +12625,7 @@
         <v>20920.025594999999</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529" s="3">
         <v>45739</v>
       </c>
@@ -12652,7 +12648,7 @@
         <v>20231.5094719999</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" s="3">
         <v>45739</v>
       </c>
@@ -12675,7 +12671,7 @@
         <v>19586.416261999999</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A531" s="3">
         <v>45739</v>
       </c>
@@ -12698,7 +12694,7 @@
         <v>19078.899487999999</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532" s="3">
         <v>45739</v>
       </c>
@@ -12721,7 +12717,7 @@
         <v>18614.860135999999</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533" s="3">
         <v>45739</v>
       </c>
@@ -12744,7 +12740,7 @@
         <v>18530.712122000001</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A534" s="3">
         <v>45739</v>
       </c>
@@ -12767,7 +12763,7 @@
         <v>18691.489441999998</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A535" s="3">
         <v>45739</v>
       </c>
@@ -12790,7 +12786,7 @@
         <v>19395.993224999998</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A536" s="3">
         <v>45739</v>
       </c>
@@ -12813,7 +12809,7 @@
         <v>20014.592352</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A537" s="3">
         <v>45739</v>
       </c>
@@ -12836,7 +12832,7 @@
         <v>20057.79695145</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A538" s="3">
         <v>45739</v>
       </c>
@@ -12859,7 +12855,7 @@
         <v>19441.627681999998</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A539" s="3">
         <v>45739</v>
       </c>
@@ -12882,7 +12878,7 @@
         <v>18184.996477000001</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A540" s="3">
         <v>45739</v>
       </c>
@@ -12905,7 +12901,7 @@
         <v>17496.027209</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A541" s="3">
         <v>45739</v>
       </c>
@@ -12928,7 +12924,7 @@
         <v>17098.808811999999</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A542" s="3">
         <v>45739</v>
       </c>
@@ -12951,7 +12947,7 @@
         <v>16960.141039999999</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A543" s="3">
         <v>45739</v>
       </c>
@@ -12974,7 +12970,7 @@
         <v>16611.6639059999</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A544" s="3">
         <v>45739</v>
       </c>
@@ -12997,7 +12993,7 @@
         <v>17317.790153999998</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A545" s="3">
         <v>45739</v>
       </c>
@@ -13020,7 +13016,7 @@
         <v>18093.311507999999</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A546" s="3">
         <v>45739</v>
       </c>
@@ -13043,7 +13039,7 @@
         <v>19704.682825200001</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A547" s="3">
         <v>45739</v>
       </c>
@@ -13066,7 +13062,7 @@
         <v>22181.126737999999</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A548" s="3">
         <v>45739</v>
       </c>
@@ -13089,7 +13085,7 @@
         <v>23742.165676999899</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A549" s="3">
         <v>45739</v>
       </c>
@@ -13112,7 +13108,7 @@
         <v>23668.664446999999</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A550" s="3">
         <v>45739</v>
       </c>
@@ -13135,7 +13131,7 @@
         <v>23097.581182999998</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A551" s="3">
         <v>45739</v>
       </c>
@@ -13158,7 +13154,7 @@
         <v>21972.675674999999</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A552" s="3">
         <v>45739</v>
       </c>
@@ -13181,7 +13177,7 @@
         <v>20785.076186999999</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A553" s="3">
         <v>45740</v>
       </c>
@@ -13204,7 +13200,7 @@
         <v>20446.137719999999</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A554" s="3">
         <v>45740</v>
       </c>
@@ -13227,7 +13223,7 @@
         <v>19911.696667</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A555" s="3">
         <v>45740</v>
       </c>
@@ -13250,7 +13246,7 @@
         <v>19489.062195999999</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A556" s="3">
         <v>45740</v>
       </c>
@@ -13273,7 +13269,7 @@
         <v>19211.815497</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A557" s="3">
         <v>45740</v>
       </c>
@@ -13296,7 +13292,7 @@
         <v>19448.450422999998</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A558" s="3">
         <v>45740</v>
       </c>
@@ -13319,7 +13315,7 @@
         <v>20672.307623000001</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A559" s="3">
         <v>45740</v>
       </c>
@@ -13342,7 +13338,7 @@
         <v>22558.628863999998</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A560" s="3">
         <v>45740</v>
       </c>
@@ -13365,7 +13361,7 @@
         <v>24141.560181000001</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A561" s="3">
         <v>45740</v>
       </c>
@@ -13388,7 +13384,7 @@
         <v>24388.119460999998</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A562" s="3">
         <v>45740</v>
       </c>
@@ -13411,7 +13407,7 @@
         <v>23510.975079100001</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A563" s="3">
         <v>45740</v>
       </c>
@@ -13434,7 +13430,7 @@
         <v>22523.749503700001</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A564" s="3">
         <v>45740</v>
       </c>
@@ -13457,7 +13453,7 @@
         <v>21329.856872299999</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A565" s="3">
         <v>45740</v>
       </c>
@@ -13480,7 +13476,7 @@
         <v>20773.749756699999</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A566" s="3">
         <v>45740</v>
       </c>
@@ -13503,7 +13499,7 @@
         <v>20638.017881</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A567" s="3">
         <v>45740</v>
       </c>
@@ -13526,7 +13522,7 @@
         <v>20821.905348999899</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A568" s="3">
         <v>45740</v>
       </c>
@@ -13549,7 +13545,7 @@
         <v>22127.0943692</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A569" s="3">
         <v>45740</v>
       </c>
@@ -13572,7 +13568,7 @@
         <v>23985.3383734899</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A570" s="3">
         <v>45740</v>
       </c>
@@ -13595,7 +13591,7 @@
         <v>24359.37138</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A571" s="3">
         <v>45740</v>
       </c>
@@ -13618,7 +13614,7 @@
         <v>25839.938770000001</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A572" s="3">
         <v>45740</v>
       </c>
@@ -13641,7 +13637,7 @@
         <v>26723.836235999999</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A573" s="3">
         <v>45740</v>
       </c>
@@ -13664,7 +13660,7 @@
         <v>26045.977973000001</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A574" s="3">
         <v>45740</v>
       </c>
@@ -13687,7 +13683,7 @@
         <v>24973.485370999999</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A575" s="3">
         <v>45740</v>
       </c>
@@ -13710,7 +13706,7 @@
         <v>23424.160045000001</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A576" s="3">
         <v>45740</v>
       </c>
@@ -13733,7 +13729,7 @@
         <v>21786.131506999998</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A577" s="3">
         <v>45741</v>
       </c>
@@ -13756,7 +13752,7 @@
         <v>21026.833200000001</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A578" s="3">
         <v>45741</v>
       </c>
@@ -13779,7 +13775,7 @@
         <v>20323.454400999999</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A579" s="3">
         <v>45741</v>
       </c>
@@ -13802,7 +13798,7 @@
         <v>19443.129368999998</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A580" s="3">
         <v>45741</v>
       </c>
@@ -13825,7 +13821,7 @@
         <v>19085.316157000001</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A581" s="3">
         <v>45741</v>
       </c>
@@ -13848,7 +13844,7 @@
         <v>19515.536082999999</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A582" s="3">
         <v>45741</v>
       </c>
@@ -13871,7 +13867,7 @@
         <v>20729.151870999998</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A583" s="3">
         <v>45741</v>
       </c>
@@ -13894,7 +13890,7 @@
         <v>22689.364286</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A584" s="3">
         <v>45741</v>
       </c>
@@ -13917,7 +13913,7 @@
         <v>23969.725564</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A585" s="3">
         <v>45741</v>
       </c>
@@ -13940,7 +13936,7 @@
         <v>24262.954839399899</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A586" s="3">
         <v>45741</v>
       </c>
@@ -13963,7 +13959,7 @@
         <v>23779.1339644</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A587" s="3">
         <v>45741</v>
       </c>
@@ -13986,7 +13982,7 @@
         <v>22176.210230000001</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A588" s="3">
         <v>45741</v>
       </c>
@@ -14009,7 +14005,7 @@
         <v>22158.427856999999</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A589" s="3">
         <v>45741</v>
       </c>
@@ -14032,7 +14028,7 @@
         <v>21639.784853999899</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A590" s="3">
         <v>45741</v>
       </c>
@@ -14055,7 +14051,7 @@
         <v>21604.106852999899</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A591" s="3">
         <v>45741</v>
       </c>
@@ -14078,7 +14074,7 @@
         <v>22268.360234</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A592" s="3">
         <v>45741</v>
       </c>
@@ -14101,7 +14097,7 @@
         <v>23191.358188999999</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A593" s="3">
         <v>45741</v>
       </c>
@@ -14124,7 +14120,7 @@
         <v>24337.866958999999</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A594" s="3">
         <v>45741</v>
       </c>
@@ -14147,7 +14143,7 @@
         <v>24783.961814400001</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A595" s="3">
         <v>45741</v>
       </c>
@@ -14170,7 +14166,7 @@
         <v>26220.091225999899</v>
       </c>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A596" s="3">
         <v>45741</v>
       </c>
@@ -14193,7 +14189,7 @@
         <v>27028.595173999998</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A597" s="3">
         <v>45741</v>
       </c>
@@ -14216,7 +14212,7 @@
         <v>26599.321704999998</v>
       </c>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A598" s="3">
         <v>45741</v>
       </c>
@@ -14239,7 +14235,7 @@
         <v>25865.393467999998</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A599" s="3">
         <v>45741</v>
       </c>
@@ -14262,7 +14258,7 @@
         <v>24422.240886</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A600" s="3">
         <v>45741</v>
       </c>
@@ -14285,7 +14281,7 @@
         <v>22800.540709000001</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A601" s="3">
         <v>45742</v>
       </c>
@@ -14308,7 +14304,7 @@
         <v>22187.663067000001</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A602" s="3">
         <v>45742</v>
       </c>
@@ -14331,7 +14327,7 @@
         <v>21315.489478</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A603" s="3">
         <v>45742</v>
       </c>
@@ -14354,7 +14350,7 @@
         <v>20762.6568459999</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A604" s="3">
         <v>45742</v>
       </c>
@@ -14377,7 +14373,7 @@
         <v>20480.387845000001</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A605" s="3">
         <v>45742</v>
       </c>
@@ -14400,7 +14396,7 @@
         <v>20420.158278999999</v>
       </c>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A606" s="3">
         <v>45742</v>
       </c>
@@ -14423,7 +14419,7 @@
         <v>21381.345731000001</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A607" s="3">
         <v>45742</v>
       </c>
@@ -14446,7 +14442,7 @@
         <v>22875.908551</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A608" s="3">
         <v>45742</v>
       </c>
@@ -14469,7 +14465,7 @@
         <v>24255.5148019999</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A609" s="3">
         <v>45742</v>
       </c>
@@ -14492,7 +14488,7 @@
         <v>24501.177555999999</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A610" s="3">
         <v>45742</v>
       </c>
@@ -14515,7 +14511,7 @@
         <v>23866.119573399999</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A611" s="3">
         <v>45742</v>
       </c>
@@ -14538,7 +14534,7 @@
         <v>23997.8781109999</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A612" s="3">
         <v>45742</v>
       </c>
@@ -14561,7 +14557,7 @@
         <v>23409.149536000001</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A613" s="3">
         <v>45742</v>
       </c>
@@ -14584,7 +14580,7 @@
         <v>24017.4204509999</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A614" s="3">
         <v>45742</v>
       </c>
@@ -14607,7 +14603,7 @@
         <v>24358.202206999998</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A615" s="3">
         <v>45742</v>
       </c>
@@ -14630,7 +14626,7 @@
         <v>24469.844337999999</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A616" s="3">
         <v>45742</v>
       </c>
@@ -14653,7 +14649,7 @@
         <v>24784.007455999999</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A617" s="3">
         <v>45742</v>
       </c>
@@ -14676,7 +14672,7 @@
         <v>25063.376854999999</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A618" s="3">
         <v>45742</v>
       </c>
@@ -14699,7 +14695,7 @@
         <v>24326.176346599899</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A619" s="3">
         <v>45742</v>
       </c>
@@ -14722,7 +14718,7 @@
         <v>24642.45638</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A620" s="3">
         <v>45742</v>
       </c>
@@ -14745,7 +14741,7 @@
         <v>25780.567805999999</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A621" s="3">
         <v>45742</v>
       </c>
@@ -14768,7 +14764,7 @@
         <v>25254.218434999999</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A622" s="3">
         <v>45742</v>
       </c>
@@ -14791,7 +14787,7 @@
         <v>24530.574605000002</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A623" s="3">
         <v>45742</v>
       </c>
@@ -14814,7 +14810,7 @@
         <v>23386.526431999999</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A624" s="3">
         <v>45742</v>
       </c>
@@ -14837,7 +14833,7 @@
         <v>22221.407813000002</v>
       </c>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A625" s="3">
         <v>45743</v>
       </c>
@@ -14860,7 +14856,7 @@
         <v>21304.040297</v>
       </c>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A626" s="3">
         <v>45743</v>
       </c>
@@ -14883,7 +14879,7 @@
         <v>20610.560078999999</v>
       </c>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A627" s="3">
         <v>45743</v>
       </c>
@@ -14906,7 +14902,7 @@
         <v>20018.497374999999</v>
       </c>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A628" s="3">
         <v>45743</v>
       </c>
@@ -14929,7 +14925,7 @@
         <v>19511.904156000001</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A629" s="3">
         <v>45743</v>
       </c>
@@ -14952,7 +14948,7 @@
         <v>19324.908101000001</v>
       </c>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A630" s="3">
         <v>45743</v>
       </c>
@@ -14975,7 +14971,7 @@
         <v>20241.037106</v>
       </c>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A631" s="3">
         <v>45743</v>
       </c>
@@ -14998,7 +14994,7 @@
         <v>22247.029732999999</v>
       </c>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A632" s="3">
         <v>45743</v>
       </c>
@@ -15021,7 +15017,7 @@
         <v>23905.237311999899</v>
       </c>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A633" s="3">
         <v>45743</v>
       </c>
@@ -15044,7 +15040,7 @@
         <v>24669.131853499999</v>
       </c>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A634" s="3">
         <v>45743</v>
       </c>
@@ -15067,7 +15063,7 @@
         <v>24589.332656999999</v>
       </c>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A635" s="3">
         <v>45743</v>
       </c>
@@ -15090,7 +15086,7 @@
         <v>24231.495013</v>
       </c>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A636" s="3">
         <v>45743</v>
       </c>
@@ -15113,7 +15109,7 @@
         <v>24873.528119999999</v>
       </c>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A637" s="3">
         <v>45743</v>
       </c>
@@ -15136,7 +15132,7 @@
         <v>24564.448520999998</v>
       </c>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A638" s="3">
         <v>45743</v>
       </c>
@@ -15159,7 +15155,7 @@
         <v>24041.862702999999</v>
       </c>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A639" s="3">
         <v>45743</v>
       </c>
@@ -15182,7 +15178,7 @@
         <v>22881.675867999998</v>
       </c>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A640" s="3">
         <v>45743</v>
       </c>
@@ -15205,7 +15201,7 @@
         <v>21528.603904</v>
       </c>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A641" s="3">
         <v>45743</v>
       </c>
@@ -15228,7 +15224,7 @@
         <v>20964.754280000001</v>
       </c>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A642" s="3">
         <v>45743</v>
       </c>
@@ -15251,7 +15247,7 @@
         <v>21799.5939674</v>
       </c>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A643" s="3">
         <v>45743</v>
       </c>
@@ -15274,7 +15270,7 @@
         <v>23298.08527</v>
       </c>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A644" s="3">
         <v>45743</v>
       </c>
@@ -15297,7 +15293,7 @@
         <v>24777.885921999899</v>
       </c>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A645" s="3">
         <v>45743</v>
       </c>
@@ -15320,7 +15316,7 @@
         <v>24531.450438</v>
       </c>
     </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A646" s="3">
         <v>45743</v>
       </c>
@@ -15343,7 +15339,7 @@
         <v>23937.492963000001</v>
       </c>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A647" s="3">
         <v>45743</v>
       </c>
@@ -15366,7 +15362,7 @@
         <v>23049.346810999999</v>
       </c>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A648" s="3">
         <v>45743</v>
       </c>
@@ -15389,7 +15385,7 @@
         <v>22294.661885000001</v>
       </c>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A649" s="3">
         <v>45744</v>
       </c>
@@ -15412,7 +15408,7 @@
         <v>21844.280964000001</v>
       </c>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A650" s="3">
         <v>45744</v>
       </c>
@@ -15435,7 +15431,7 @@
         <v>20978.865519999999</v>
       </c>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A651" s="3">
         <v>45744</v>
       </c>
@@ -15458,7 +15454,7 @@
         <v>20215.179070999999</v>
       </c>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A652" s="3">
         <v>45744</v>
       </c>
@@ -15481,7 +15477,7 @@
         <v>20240.068534999999</v>
       </c>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A653" s="3">
         <v>45744</v>
       </c>
@@ -15504,7 +15500,7 @@
         <v>20623.158627999899</v>
       </c>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A654" s="3">
         <v>45744</v>
       </c>
@@ -15527,7 +15523,7 @@
         <v>21467.518134999998</v>
       </c>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A655" s="3">
         <v>45744</v>
       </c>
@@ -15550,7 +15546,7 @@
         <v>22967.565605</v>
       </c>
     </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A656" s="3">
         <v>45744</v>
       </c>
@@ -15573,7 +15569,7 @@
         <v>23685.818582</v>
       </c>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A657" s="3">
         <v>45744</v>
       </c>
@@ -15596,7 +15592,7 @@
         <v>23404.257903000002</v>
       </c>
     </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A658" s="3">
         <v>45744</v>
       </c>
@@ -15619,7 +15615,7 @@
         <v>22592.8896131</v>
       </c>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A659" s="3">
         <v>45744</v>
       </c>
@@ -15642,7 +15638,7 @@
         <v>22268.059401999999</v>
       </c>
     </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A660" s="3">
         <v>45744</v>
       </c>
@@ -15665,7 +15661,7 @@
         <v>22054.719867</v>
       </c>
     </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A661" s="3">
         <v>45744</v>
       </c>
@@ -15688,7 +15684,7 @@
         <v>23351.984289999898</v>
       </c>
     </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A662" s="3">
         <v>45744</v>
       </c>
@@ -15711,7 +15707,7 @@
         <v>23708.086216</v>
       </c>
     </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A663" s="3">
         <v>45744</v>
       </c>
@@ -15734,7 +15730,7 @@
         <v>24430.280871999999</v>
       </c>
     </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A664" s="3">
         <v>45744</v>
       </c>
@@ -15757,7 +15753,7 @@
         <v>23571.532803999999</v>
       </c>
     </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A665" s="3">
         <v>45744</v>
       </c>
@@ -15780,7 +15776,7 @@
         <v>22928.784645</v>
       </c>
     </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A666" s="3">
         <v>45744</v>
       </c>
@@ -15803,7 +15799,7 @@
         <v>22471.9325079999</v>
       </c>
     </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A667" s="3">
         <v>45744</v>
       </c>
@@ -15826,7 +15822,7 @@
         <v>23161.098309999899</v>
       </c>
     </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A668" s="3">
         <v>45744</v>
       </c>
@@ -15849,7 +15845,7 @@
         <v>24459.254420000001</v>
       </c>
     </row>
-    <row r="669" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A669" s="3">
         <v>45744</v>
       </c>
@@ -15872,7 +15868,7 @@
         <v>24524.984732999899</v>
       </c>
     </row>
-    <row r="670" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A670" s="3">
         <v>45744</v>
       </c>
@@ -15895,7 +15891,7 @@
         <v>24185.270863999998</v>
       </c>
     </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A671" s="3">
         <v>45744</v>
       </c>
@@ -15918,7 +15914,7 @@
         <v>23273.131557000001</v>
       </c>
     </row>
-    <row r="672" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A672" s="3">
         <v>45744</v>
       </c>
@@ -15941,7 +15937,7 @@
         <v>22443.665988000001</v>
       </c>
     </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A673" s="3">
         <v>45745</v>
       </c>
@@ -15964,7 +15960,7 @@
         <v>21478.528511</v>
       </c>
     </row>
-    <row r="674" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A674" s="3">
         <v>45745</v>
       </c>
@@ -15987,7 +15983,7 @@
         <v>20850.53559</v>
       </c>
     </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A675" s="3">
         <v>45745</v>
       </c>
@@ -16010,7 +16006,7 @@
         <v>20253.179507000001</v>
       </c>
     </row>
-    <row r="676" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A676" s="3">
         <v>45745</v>
       </c>
@@ -16033,7 +16029,7 @@
         <v>19721.715276999999</v>
       </c>
     </row>
-    <row r="677" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A677" s="3">
         <v>45745</v>
       </c>
@@ -16056,7 +16052,7 @@
         <v>19582.789150000001</v>
       </c>
     </row>
-    <row r="678" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A678" s="3">
         <v>45745</v>
       </c>
@@ -16079,7 +16075,7 @@
         <v>19869.169900000001</v>
       </c>
     </row>
-    <row r="679" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A679" s="3">
         <v>45745</v>
       </c>
@@ -16102,7 +16098,7 @@
         <v>20644.792723999999</v>
       </c>
     </row>
-    <row r="680" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A680" s="3">
         <v>45745</v>
       </c>
@@ -16125,7 +16121,7 @@
         <v>21043.689364000002</v>
       </c>
     </row>
-    <row r="681" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A681" s="3">
         <v>45745</v>
       </c>
@@ -16148,7 +16144,7 @@
         <v>21242.009466</v>
       </c>
     </row>
-    <row r="682" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A682" s="3">
         <v>45745</v>
       </c>
@@ -16171,7 +16167,7 @@
         <v>21072.434255</v>
       </c>
     </row>
-    <row r="683" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A683" s="3">
         <v>45745</v>
       </c>
@@ -16194,7 +16190,7 @@
         <v>19731.833362000001</v>
       </c>
     </row>
-    <row r="684" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A684" s="3">
         <v>45745</v>
       </c>
@@ -16217,7 +16213,7 @@
         <v>19205.008263</v>
       </c>
     </row>
-    <row r="685" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A685" s="3">
         <v>45745</v>
       </c>
@@ -16240,7 +16236,7 @@
         <v>18375.190720999999</v>
       </c>
     </row>
-    <row r="686" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A686" s="3">
         <v>45745</v>
       </c>
@@ -16263,7 +16259,7 @@
         <v>17422.412483</v>
       </c>
     </row>
-    <row r="687" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A687" s="3">
         <v>45745</v>
       </c>
@@ -16286,7 +16282,7 @@
         <v>17636.1860219999</v>
       </c>
     </row>
-    <row r="688" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A688" s="3">
         <v>45745</v>
       </c>
@@ -16309,7 +16305,7 @@
         <v>17772.230470999999</v>
       </c>
     </row>
-    <row r="689" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A689" s="3">
         <v>45745</v>
       </c>
@@ -16332,7 +16328,7 @@
         <v>18407.043762000001</v>
       </c>
     </row>
-    <row r="690" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A690" s="3">
         <v>45745</v>
       </c>
@@ -16355,7 +16351,7 @@
         <v>19827.119152499999</v>
       </c>
     </row>
-    <row r="691" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A691" s="3">
         <v>45745</v>
       </c>
@@ -16378,7 +16374,7 @@
         <v>21818.168631</v>
       </c>
     </row>
-    <row r="692" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A692" s="3">
         <v>45745</v>
       </c>
@@ -16401,7 +16397,7 @@
         <v>22793.0461489999</v>
       </c>
     </row>
-    <row r="693" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A693" s="3">
         <v>45745</v>
       </c>
@@ -16424,7 +16420,7 @@
         <v>23206.272373</v>
       </c>
     </row>
-    <row r="694" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A694" s="3">
         <v>45745</v>
       </c>
@@ -16447,7 +16443,7 @@
         <v>22861.190847999998</v>
       </c>
     </row>
-    <row r="695" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A695" s="3">
         <v>45745</v>
       </c>
@@ -16470,7 +16466,7 @@
         <v>22026.903846000001</v>
       </c>
     </row>
-    <row r="696" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A696" s="3">
         <v>45745</v>
       </c>
@@ -16493,7 +16489,7 @@
         <v>21185.450852999998</v>
       </c>
     </row>
-    <row r="697" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A697" s="3">
         <v>45746</v>
       </c>
@@ -16516,7 +16512,7 @@
         <v>20951.082973999899</v>
       </c>
     </row>
-    <row r="698" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A698" s="3">
         <v>45746</v>
       </c>
@@ -16539,7 +16535,7 @@
         <v>20209.159790000002</v>
       </c>
     </row>
-    <row r="699" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A699" s="3">
         <v>45746</v>
       </c>
@@ -16562,7 +16558,7 @@
         <v>19596.978523999998</v>
       </c>
     </row>
-    <row r="700" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A700" s="3">
         <v>45746</v>
       </c>
@@ -16585,7 +16581,7 @@
         <v>19577.908719999999</v>
       </c>
     </row>
-    <row r="701" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A701" s="3">
         <v>45746</v>
       </c>
@@ -16608,7 +16604,7 @@
         <v>18918.370954999999</v>
       </c>
     </row>
-    <row r="702" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A702" s="3">
         <v>45746</v>
       </c>
@@ -16631,7 +16627,7 @@
         <v>18984.235392999999</v>
       </c>
     </row>
-    <row r="703" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A703" s="3">
         <v>45746</v>
       </c>
@@ -16654,7 +16650,7 @@
         <v>19416.453291999998</v>
       </c>
     </row>
-    <row r="704" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A704" s="3">
         <v>45746</v>
       </c>
@@ -16677,7 +16673,7 @@
         <v>20079.462813999999</v>
       </c>
     </row>
-    <row r="705" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A705" s="3">
         <v>45746</v>
       </c>
@@ -16700,7 +16696,7 @@
         <v>20257.837169800001</v>
       </c>
     </row>
-    <row r="706" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A706" s="3">
         <v>45746</v>
       </c>
@@ -16723,7 +16719,7 @@
         <v>21554.282286000001</v>
       </c>
     </row>
-    <row r="707" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A707" s="3">
         <v>45746</v>
       </c>
@@ -16746,7 +16742,7 @@
         <v>21267.588358000001</v>
       </c>
     </row>
-    <row r="708" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A708" s="3">
         <v>45746</v>
       </c>
@@ -16769,7 +16765,7 @@
         <v>22710.710927</v>
       </c>
     </row>
-    <row r="709" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A709" s="3">
         <v>45746</v>
       </c>
@@ -16792,7 +16788,7 @@
         <v>22757.599869199999</v>
       </c>
     </row>
-    <row r="710" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A710" s="3">
         <v>45746</v>
       </c>
@@ -16815,7 +16811,7 @@
         <v>21994.216109000001</v>
       </c>
     </row>
-    <row r="711" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A711" s="3">
         <v>45746</v>
       </c>
@@ -16838,7 +16834,7 @@
         <v>20868.324615599999</v>
       </c>
     </row>
-    <row r="712" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A712" s="3">
         <v>45746</v>
       </c>
@@ -16861,7 +16857,7 @@
         <v>19912.966423000002</v>
       </c>
     </row>
-    <row r="713" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A713" s="3">
         <v>45746</v>
       </c>
@@ -16884,7 +16880,7 @@
         <v>19981.464509000001</v>
       </c>
     </row>
-    <row r="714" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A714" s="3">
         <v>45746</v>
       </c>
@@ -16907,7 +16903,7 @@
         <v>20088.246708400002</v>
       </c>
     </row>
-    <row r="715" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A715" s="3">
         <v>45746</v>
       </c>
@@ -16930,7 +16926,7 @@
         <v>21788.059352</v>
       </c>
     </row>
-    <row r="716" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A716" s="3">
         <v>45746</v>
       </c>
@@ -16953,7 +16949,7 @@
         <v>23408.738651</v>
       </c>
     </row>
-    <row r="717" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A717" s="3">
         <v>45746</v>
       </c>
@@ -16976,7 +16972,7 @@
         <v>23542.510629</v>
       </c>
     </row>
-    <row r="718" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A718" s="3">
         <v>45746</v>
       </c>
@@ -16999,7 +16995,7 @@
         <v>23184.862084</v>
       </c>
     </row>
-    <row r="719" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A719" s="3">
         <v>45746</v>
       </c>
@@ -17022,7 +17018,7 @@
         <v>22294.254948000002</v>
       </c>
     </row>
-    <row r="720" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A720" s="3">
         <v>45746</v>
       </c>
@@ -17045,7 +17041,7 @@
         <v>21562.579793000001</v>
       </c>
     </row>
-    <row r="721" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A721" s="3">
         <v>45747</v>
       </c>
@@ -17068,7 +17064,7 @@
         <v>20844.262463999999</v>
       </c>
     </row>
-    <row r="722" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A722" s="3">
         <v>45747</v>
       </c>
@@ -17091,7 +17087,7 @@
         <v>20314.494494999999</v>
       </c>
     </row>
-    <row r="723" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A723" s="3">
         <v>45747</v>
       </c>
@@ -17114,7 +17110,7 @@
         <v>19728.329677999998</v>
       </c>
     </row>
-    <row r="724" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A724" s="3">
         <v>45747</v>
       </c>
@@ -17137,7 +17133,7 @@
         <v>19246.931398000001</v>
       </c>
     </row>
-    <row r="725" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A725" s="3">
         <v>45747</v>
       </c>
@@ -17160,7 +17156,7 @@
         <v>19395.232238000001</v>
       </c>
     </row>
-    <row r="726" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A726" s="3">
         <v>45747</v>
       </c>
@@ -17183,7 +17179,7 @@
         <v>20681.220824</v>
       </c>
     </row>
-    <row r="727" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A727" s="3">
         <v>45747</v>
       </c>
@@ -17206,7 +17202,7 @@
         <v>22540.355388</v>
       </c>
     </row>
-    <row r="728" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A728" s="3">
         <v>45747</v>
       </c>
@@ -17229,7 +17225,7 @@
         <v>24156.282767999899</v>
       </c>
     </row>
-    <row r="729" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A729" s="3">
         <v>45747</v>
       </c>
@@ -17252,7 +17248,7 @@
         <v>24294.942002999898</v>
       </c>
     </row>
-    <row r="730" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A730" s="3">
         <v>45747</v>
       </c>
@@ -17275,7 +17271,7 @@
         <v>25422.690954000002</v>
       </c>
     </row>
-    <row r="731" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A731" s="3">
         <v>45747</v>
       </c>
@@ -17298,7 +17294,7 @@
         <v>25081.496992799999</v>
       </c>
     </row>
-    <row r="732" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A732" s="3">
         <v>45747</v>
       </c>
@@ -17321,7 +17317,7 @@
         <v>26523.96675</v>
       </c>
     </row>
-    <row r="733" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A733" s="3">
         <v>45747</v>
       </c>
@@ -17344,7 +17340,7 @@
         <v>26216.329891400001</v>
       </c>
     </row>
-    <row r="734" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A734" s="3">
         <v>45747</v>
       </c>
@@ -17367,7 +17363,7 @@
         <v>25434.289108199999</v>
       </c>
     </row>
-    <row r="735" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A735" s="3">
         <v>45747</v>
       </c>
@@ -17390,7 +17386,7 @@
         <v>25227.928464199998</v>
       </c>
     </row>
-    <row r="736" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A736" s="3">
         <v>45747</v>
       </c>
@@ -17413,7 +17409,7 @@
         <v>24531.191138099999</v>
       </c>
     </row>
-    <row r="737" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A737" s="3">
         <v>45747</v>
       </c>
@@ -17436,7 +17432,7 @@
         <v>24794.304511999999</v>
       </c>
     </row>
-    <row r="738" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A738" s="3">
         <v>45747</v>
       </c>
@@ -17459,7 +17455,7 @@
         <v>23520.4662719999</v>
       </c>
     </row>
-    <row r="739" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A739" s="3">
         <v>45747</v>
       </c>
@@ -17482,7 +17478,7 @@
         <v>24302.354702999899</v>
       </c>
     </row>
-    <row r="740" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A740" s="3">
         <v>45747</v>
       </c>
@@ -17505,7 +17501,7 @@
         <v>25501.243046</v>
       </c>
     </row>
-    <row r="741" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A741" s="3">
         <v>45747</v>
       </c>
@@ -17528,7 +17524,7 @@
         <v>25553.709425999899</v>
       </c>
     </row>
-    <row r="742" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A742" s="3">
         <v>45747</v>
       </c>
@@ -17551,7 +17547,7 @@
         <v>25001.932055000001</v>
       </c>
     </row>
-    <row r="743" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A743" s="3">
         <v>45747</v>
       </c>
@@ -17574,7 +17570,7 @@
         <v>23733.659701</v>
       </c>
     </row>
-    <row r="744" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A744" s="3">
         <v>45747</v>
       </c>
@@ -17597,7 +17593,7 @@
         <v>22490.032432</v>
       </c>
     </row>
-    <row r="746" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A746" s="7" t="s">
         <v>7</v>
       </c>
@@ -17612,246 +17608,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010040508A287E7EBD4494AB2CE873AD2C03" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f7b5e15bc5257a07a85159909b0094b7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dcc7e218-8b47-4273-ba28-07719656e1ad" xmlns:ns3="2e64aaae-efe8-4b36-9ab4-486f04499e09" xmlns:ns4="e6671a59-50a7-4167-890c-836f7535b734" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="861cdd654f628490d9d5c0d8d3dc1a8b" ns2:_="" ns3:_="" ns4:_="">
-    <xsd:import namespace="dcc7e218-8b47-4273-ba28-07719656e1ad"/>
-    <xsd:import namespace="2e64aaae-efe8-4b36-9ab4-486f04499e09"/>
-    <xsd:import namespace="e6671a59-50a7-4167-890c-836f7535b734"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:_dlc_DocId" minOccurs="0"/>
-                <xsd:element ref="ns2:_dlc_DocIdUrl" minOccurs="0"/>
-                <xsd:element ref="ns2:_dlc_DocIdPersistId" minOccurs="0"/>
-                <xsd:element ref="ns3:b096d808b59a41b7a526eb1052d792f3" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAllLabel" minOccurs="0"/>
-                <xsd:element ref="ns3:ac6042663e6544a5b5f6c47baa21cbec" minOccurs="0"/>
-                <xsd:element ref="ns3:mb7a63be961241008d728fcf8db72869" minOccurs="0"/>
-                <xsd:element ref="ns4:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns4:SharedWithDetails" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dcc7e218-8b47-4273-ba28-07719656e1ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:internalName="_dlc_DocId" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:URL">
-            <xsd:sequence>
-              <xsd:element name="Url" type="dms:ValidUrl" minOccurs="0" nillable="true"/>
-              <xsd:element name="Description" type="xsd:string" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="_dlc_DocIdPersistId" ma:index="10" nillable="true" ma:displayName="Persist ID" ma:description="Keep ID on add." ma:hidden="true" ma:internalName="_dlc_DocIdPersistId" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2e64aaae-efe8-4b36-9ab4-486f04499e09" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="b096d808b59a41b7a526eb1052d792f3" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="b096d808b59a41b7a526eb1052d792f3" ma:taxonomyFieldName="AutoClassRecordSeries" ma:displayName="Automatically Updated Record Series" ma:readOnly="false" ma:default="" ma:fieldId="{b096d808-b59a-41b7-a526-eb1052d792f3}" ma:sspId="2e7ee6ce-ef65-4ea8-ac93-b3dccb6c50ab" ma:termSetId="7d168031-9c36-4bb0-a326-5d21d4010fef" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:description="" ma:hidden="true" ma:list="{379d5730-78e4-4cbb-96dd-e465d29e98e0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e6671a59-50a7-4167-890c-836f7535b734">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAllLabel" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column1" ma:description="" ma:hidden="true" ma:list="{379d5730-78e4-4cbb-96dd-e465d29e98e0}" ma:internalName="TaxCatchAllLabel" ma:readOnly="true" ma:showField="CatchAllDataLabel" ma:web="e6671a59-50a7-4167-890c-836f7535b734">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="ac6042663e6544a5b5f6c47baa21cbec" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="ac6042663e6544a5b5f6c47baa21cbec" ma:taxonomyFieldName="AutoClassDocumentType" ma:displayName="Automatically Updated Document Type" ma:readOnly="false" ma:default="" ma:fieldId="{ac604266-3e65-44a5-b5f6-c47baa21cbec}" ma:sspId="2e7ee6ce-ef65-4ea8-ac93-b3dccb6c50ab" ma:termSetId="0970d2fb-dc85-4fb5-b352-cf8dd925641e" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="mb7a63be961241008d728fcf8db72869" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="mb7a63be961241008d728fcf8db72869" ma:taxonomyFieldName="AutoClassTopic" ma:displayName="Automatically Updated Topic" ma:readOnly="false" ma:default="" ma:fieldId="{6b7a63be-9612-4100-8d72-8fcf8db72869}" ma:taxonomyMulti="true" ma:sspId="2e7ee6ce-ef65-4ea8-ac93-b3dccb6c50ab" ma:termSetId="8b5665c4-6659-459b-90b1-69777ba5afad" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e6671a59-50a7-4167-890c-836f7535b734" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100776092249CC62C48AA17033F357BFB4B" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f85f54304d83be0e0a0a7c504015390c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f573df0eeabf3db2078929eed011e841">
     <xsd:element name="properties">
@@ -17965,13 +17721,38 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C7B6BA-85D6-4D5E-932A-0B88FF44EADE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7048AD2F-A120-4F92-B8B4-50D722368C95}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -17979,31 +17760,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F689AE7E-96B6-4B9D-9FE6-78C825519F96}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="dcc7e218-8b47-4273-ba28-07719656e1ad"/>
-    <ds:schemaRef ds:uri="2e64aaae-efe8-4b36-9ab4-486f04499e09"/>
-    <ds:schemaRef ds:uri="e6671a59-50a7-4167-890c-836f7535b734"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C7B6BA-85D6-4D5E-932A-0B88FF44EADE}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF84784E-56B2-46F5-B48A-7785015432C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
